--- a/input/01_input_bapp_t1_pml.xlsx
+++ b/input/01_input_bapp_t1_pml.xlsx
@@ -42,7 +42,7 @@
     <t>B-040/SPK-PML-SE2026/6304/PL.200/2026</t>
   </si>
   <si>
-    <t>https://drive.google.com/open?id=1hAoF6SIOIoAI2ev75Kcmh9uqs8z1km4D</t>
+    <t>https://example.go.id/api/dokumen/123/gambar</t>
   </si>
   <si>
     <t>no_urut_bapp_t1</t>
